--- a/budgets/Budget.xlsx
+++ b/budgets/Budget.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jhrg/src/opendap/ESDS_AI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jhrg/src/opendap/ESDS_AI/budgets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7F9DCA3-F5DB-6D41-A4EE-FE0D7971FEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67B8E69-9AF6-8040-A851-68BAA4370E7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23660" yWindow="1400" windowWidth="28040" windowHeight="17180" xr2:uid="{5EE2F73C-A965-2049-AC5D-3BBF6DF8A5C1}"/>
+    <workbookView xWindow="22060" yWindow="1400" windowWidth="28040" windowHeight="17180" xr2:uid="{5EE2F73C-A965-2049-AC5D-3BBF6DF8A5C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
